--- a/data/trans_dic/P21D_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,16</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3690</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2689</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2439</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 3836</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>0; 3635</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1163</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1641</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3789</t>
+          <t>0; 2966</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>0; 3452</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1235</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1063</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1175</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1031</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4422</t>
+          <t>0; 4426</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5358</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Edad-trans_dic.xlsx
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3635</t>
+          <t>0; 3354</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2966</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 3546</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4426</t>
+          <t>0; 5349</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5358</t>
+          <t>0; 5120</t>
         </is>
       </c>
     </row>
